--- a/data/program-participants.xlsx
+++ b/data/program-participants.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Geet Ramayan (example)</t>
+          <t>Geet Ramayan</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Geet Ramayan (example)</t>
+          <t>Geet Ramayan</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abhangvani (example)</t>
+          <t>Abhangvani</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -501,7 +501,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Abhangvani (example)</t>
+          <t>Abhangvani</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
